--- a/8035.T_settings.xlsx
+++ b/8035.T_settings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AverageProfit</t>
+          <t>ProfitPerTrade</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -464,12 +464,27 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>FinalCapital</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TotalCommission</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AverageHoldDays</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>MaxDrawdown</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Eligible</t>
         </is>
       </c>
     </row>
@@ -482,42 +497,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F2" t="n">
-        <v>30.71500426906072</v>
+        <v>38.20006315091974</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>15.36%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>307,150円</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>25日</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.244451461213305</v>
+      </c>
+      <c r="I2" t="n">
+        <v>382000.6315091974</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1382000.631509197</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18266.8790059359</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14.29560188636126</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -525,46 +541,47 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F3" t="n">
-        <v>26.86185995790114</v>
+        <v>38.06323721854407</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>13.43%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>268,619円</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>26日</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.229248579838231</v>
+      </c>
+      <c r="I3" t="n">
+        <v>380632.3721854407</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1380632.372185441</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18255.30263463021</v>
+      </c>
+      <c r="L3" t="n">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14.380454120964</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -576,42 +593,43 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F4" t="n">
-        <v>26.26317702653581</v>
+        <v>38.06323721854407</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>26.26%</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>262,632円</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>29日</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.229248579838231</v>
+      </c>
+      <c r="I4" t="n">
+        <v>380632.3721854407</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1380632.372185441</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18255.30263463021</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14.380454120964</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -619,7 +637,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -628,37 +646,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F5" t="n">
-        <v>26.26317702653581</v>
+        <v>34.07345436450285</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>26.26%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>262,632円</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>29日</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.78593937383365</v>
+      </c>
+      <c r="I5" t="n">
+        <v>340734.5436450285</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1340734.543645028</v>
+      </c>
+      <c r="K5" t="n">
+        <v>17863.62056441342</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="M5" t="n">
+        <v>16.85470724584358</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -666,46 +685,47 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F6" t="n">
-        <v>26.26317702653581</v>
+        <v>34.07345436450285</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>26.26%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>262,632円</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>29日</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.78593937383365</v>
+      </c>
+      <c r="I6" t="n">
+        <v>340734.5436450285</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1340734.543645028</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17863.62056441342</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16.85470724584358</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -713,46 +733,47 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F7" t="n">
-        <v>22.41003271537623</v>
+        <v>33.94071400981706</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>22.41%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>224,100円</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.771190445535229</v>
+      </c>
+      <c r="I7" t="n">
+        <v>339407.1400981706</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1339407.140098171</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17852.38985977717</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10.44444444444444</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -760,46 +781,47 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>22.41003271537623</v>
+        <v>33.94071400981706</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>22.41%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>224,100円</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.771190445535229</v>
+      </c>
+      <c r="I8" t="n">
+        <v>339407.1400981706</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1339407.140098171</v>
+      </c>
+      <c r="K8" t="n">
+        <v>17852.38985977717</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10.44444444444444</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -811,42 +833,43 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>22.41003271537623</v>
+        <v>33.94071400981706</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>22.41%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>224,100円</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.771190445535229</v>
+      </c>
+      <c r="I9" t="n">
+        <v>339407.1400981706</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1339407.140098171</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17852.38985977717</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10.44444444444444</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -854,46 +877,47 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="F10" t="n">
-        <v>20.42470813995756</v>
+        <v>33.94071400981706</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>10.21%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>204,247円</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.771190445535229</v>
+      </c>
+      <c r="I10" t="n">
+        <v>339407.1400981706</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1339407.140098171</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17852.38985977717</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10.44444444444444</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -905,42 +929,43 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>19.86891635536322</v>
+        <v>30.03086691657931</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>9.93%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>198,689円</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.753858364572414</v>
+      </c>
+      <c r="I11" t="n">
+        <v>300308.6691657931</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1300308.669165793</v>
+      </c>
+      <c r="K11" t="n">
+        <v>15946.10145062129</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.380454120964</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -948,46 +973,47 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>18.3206106870229</v>
+        <v>28.60481757528363</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>18.32%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>183,206円</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>39日</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.860481757528363</v>
+      </c>
+      <c r="I12" t="n">
+        <v>286048.1757528363</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1286048.175752836</v>
+      </c>
+      <c r="K12" t="n">
+        <v>19408.64859621221</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14.56706195130362</v>
+      </c>
+      <c r="N12" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -999,42 +1025,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>18.3206106870229</v>
+        <v>26.14818766383985</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>18.32%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>183,206円</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>39日</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.268523457979981</v>
+      </c>
+      <c r="I13" t="n">
+        <v>261481.8766383985</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1261481.876638399</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15612.14066955373</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1042,46 +1069,47 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>18.3206106870229</v>
+        <v>26.14818766383985</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>18.32%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>183,206円</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>39日</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.268523457979981</v>
+      </c>
+      <c r="I14" t="n">
+        <v>261481.8766383985</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1261481.876638399</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15612.14066955373</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>16.93702582041117</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1089,46 +1117,47 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>16.85449957947856</v>
+        <v>24.76471969050802</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>16.85%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>168,545円</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>32日</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.476471969050802</v>
+      </c>
+      <c r="I15" t="n">
+        <v>247647.1969050802</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1247647.19690508</v>
+      </c>
+      <c r="K15" t="n">
+        <v>18971.29728732141</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>17.11806160183318</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1136,46 +1165,47 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(50, 60)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>16.85449957947856</v>
+        <v>24.76471969050802</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>16.85%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>168,545円</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>32日</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.476471969050802</v>
+      </c>
+      <c r="I16" t="n">
+        <v>247647.1969050802</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1247647.19690508</v>
+      </c>
+      <c r="K16" t="n">
+        <v>18971.29728732141</v>
+      </c>
+      <c r="L16" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17.11806160183318</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1183,46 +1213,47 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F17" t="n">
-        <v>16.85449957947856</v>
+        <v>11.46245750456799</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>16.85%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>168,545円</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>32日</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6368031946982219</v>
+      </c>
+      <c r="I17" t="n">
+        <v>114624.5750456799</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1114624.57504568</v>
+      </c>
+      <c r="K17" t="n">
+        <v>34409.26109325193</v>
+      </c>
+      <c r="L17" t="n">
+        <v>9.277777777777779</v>
+      </c>
+      <c r="M17" t="n">
+        <v>35.30659081991354</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1230,46 +1261,47 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F18" t="n">
-        <v>16.302894488248</v>
+        <v>9.033069517362955</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>8.15%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>163,029円</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>30日</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5645668448351847</v>
+      </c>
+      <c r="I18" t="n">
+        <v>90330.69517362956</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1090330.69517363</v>
+      </c>
+      <c r="K18" t="n">
+        <v>26942.44238292757</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31.33475137788361</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1277,46 +1309,47 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="F19" t="n">
-        <v>13.28847771236333</v>
+        <v>7.873218058275408</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>13.29%</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>132,885円</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>33日</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4374010032375227</v>
+      </c>
+      <c r="I19" t="n">
+        <v>78732.18058275408</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1078732.180582754</v>
+      </c>
+      <c r="K19" t="n">
+        <v>33550.6733925162</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9.333333333333334</v>
+      </c>
+      <c r="M19" t="n">
+        <v>37.38980467812942</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1328,42 +1361,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F20" t="n">
-        <v>13.28847771236333</v>
+        <v>7.594015899451007</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>13.29%</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>132,885円</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>33日</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4746259937156879</v>
+      </c>
+      <c r="I20" t="n">
+        <v>75940.15899451007</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1075940.15899451</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28920.38345350993</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9.125</v>
+      </c>
+      <c r="M20" t="n">
+        <v>32.45245999312358</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1371,7 +1405,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1380,37 +1414,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F21" t="n">
-        <v>13.28847771236333</v>
+        <v>5.777377642685525</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>13.29%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>132,885円</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>33日</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3610861026678453</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57773.77642685524</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1057773.776426855</v>
+      </c>
+      <c r="K21" t="n">
+        <v>26472.44847657669</v>
+      </c>
+      <c r="L21" t="n">
+        <v>7.6875</v>
+      </c>
+      <c r="M21" t="n">
+        <v>33.38507329398935</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1418,46 +1453,47 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F22" t="n">
-        <v>10.20277988742738</v>
+        <v>5.777377642685525</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>5.10%</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>102,028円</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>36日</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3610861026678453</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57773.77642685524</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1057773.776426855</v>
+      </c>
+      <c r="K22" t="n">
+        <v>26472.44847657669</v>
+      </c>
+      <c r="L22" t="n">
+        <v>7.6875</v>
+      </c>
+      <c r="M22" t="n">
+        <v>33.38507329398935</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1465,46 +1501,47 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F23" t="n">
-        <v>9.503784693019345</v>
+        <v>4.90092899191645</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>9.50%</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>95,038円</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>42日</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3500663565654607</v>
+      </c>
+      <c r="I23" t="n">
+        <v>49009.2899191645</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1049009.289919164</v>
+      </c>
+      <c r="K23" t="n">
+        <v>23555.25089685791</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8.214285714285714</v>
+      </c>
+      <c r="M23" t="n">
+        <v>31.33475137788361</v>
+      </c>
+      <c r="N23" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1512,46 +1549,47 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>9.503784693019345</v>
+        <v>4.374879535508051</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>9.50%</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>95,038円</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>42日</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2430488630837806</v>
+      </c>
+      <c r="I24" t="n">
+        <v>43748.79535508051</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1043748.795355081</v>
+      </c>
+      <c r="K24" t="n">
+        <v>31971.48741655216</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8.722222222222221</v>
+      </c>
+      <c r="M24" t="n">
+        <v>34.67898877759329</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1563,42 +1601,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(60, 70)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="F25" t="n">
-        <v>9.503784693019345</v>
+        <v>4.129345420285268</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>9.50%</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>95,038円</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>42日</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2580840887678292</v>
+      </c>
+      <c r="I25" t="n">
+        <v>41293.45420285268</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1041293.454202853</v>
+      </c>
+      <c r="K25" t="n">
+        <v>28157.68041025702</v>
+      </c>
+      <c r="L25" t="n">
+        <v>9.1875</v>
+      </c>
+      <c r="M25" t="n">
+        <v>34.62758066173772</v>
+      </c>
+      <c r="N25" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1606,46 +1645,47 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>66.66666666666666</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F26" t="n">
-        <v>8.796601676378479</v>
+        <v>3.047774873863801</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2.93%</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>87,966円</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>15日</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1792808749331647</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30477.74873863801</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1030477.748738638</v>
+      </c>
+      <c r="K26" t="n">
+        <v>29885.15512715251</v>
+      </c>
+      <c r="L26" t="n">
+        <v>9.235294117647058</v>
+      </c>
+      <c r="M26" t="n">
+        <v>35.30659081991354</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1653,46 +1693,47 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>66.66666666666666</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F27" t="n">
-        <v>8.796601676378479</v>
+        <v>1.768621484874177</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2.93%</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>87,966円</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>15日</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1263301060624412</v>
+      </c>
+      <c r="I27" t="n">
+        <v>17686.21484874177</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1017686.214848742</v>
+      </c>
+      <c r="K27" t="n">
+        <v>23186.39742292801</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8.428571428571429</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33.38507329398935</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1700,46 +1741,47 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(5, 20, 60)</t>
+          <t>(20, 50, 100)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>66.66666666666666</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="F28" t="n">
-        <v>6.448871886788225</v>
+        <v>1.768621484874177</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2.15%</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>64,489円</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>15日</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1263301060624412</v>
+      </c>
+      <c r="I28" t="n">
+        <v>17686.21484874177</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1017686.214848742</v>
+      </c>
+      <c r="K28" t="n">
+        <v>23186.39742292801</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8.428571428571429</v>
+      </c>
+      <c r="M28" t="n">
+        <v>33.38507329398935</v>
+      </c>
+      <c r="N28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1747,46 +1789,47 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(5, 25, 75)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>31.25</v>
       </c>
       <c r="F29" t="n">
-        <v>4.344774433853562</v>
+        <v>0.7524210363520543</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.04702631477200339</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7524.210363520542</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1007524.210363521</v>
+      </c>
+      <c r="K29" t="n">
+        <v>26772.15630211123</v>
+      </c>
+      <c r="L29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M29" t="n">
+        <v>31.79716953000986</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1798,42 +1841,43 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>35.29411764705883</v>
       </c>
       <c r="F30" t="n">
-        <v>4.344774433853562</v>
+        <v>-0.2705005949396058</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.01591179970232975</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-2705.005949396058</v>
+      </c>
+      <c r="J30" t="n">
+        <v>997294.9940506039</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29091.38515225976</v>
+      </c>
+      <c r="L30" t="n">
+        <v>9.294117647058824</v>
+      </c>
+      <c r="M30" t="n">
+        <v>37.38980467812942</v>
+      </c>
+      <c r="N30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1850,37 +1894,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(55, 65)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="F31" t="n">
-        <v>4.344774433853562</v>
+        <v>-3.504737562233431</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.2061610330725548</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-35047.37562233431</v>
+      </c>
+      <c r="J31" t="n">
+        <v>964952.6243776657</v>
+      </c>
+      <c r="K31" t="n">
+        <v>27631.41733369237</v>
+      </c>
+      <c r="L31" t="n">
+        <v>8.647058823529411</v>
+      </c>
+      <c r="M31" t="n">
+        <v>34.67898877759329</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1892,42 +1937,43 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F32" t="n">
-        <v>4.344774433853562</v>
+        <v>-21.7040919193398</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.8681636767735919</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-217040.919193398</v>
+      </c>
+      <c r="J32" t="n">
+        <v>782959.080806602</v>
+      </c>
+      <c r="K32" t="n">
+        <v>48569.94437700919</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="M32" t="n">
+        <v>28.6381981200517</v>
+      </c>
+      <c r="N32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1935,7 +1981,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1944,37 +1990,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F33" t="n">
-        <v>4.344774433853562</v>
+        <v>-24.22533050415007</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.9690132201660029</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-242253.3050415007</v>
+      </c>
+      <c r="J33" t="n">
+        <v>757746.6949584993</v>
+      </c>
+      <c r="K33" t="n">
+        <v>47172.91696193137</v>
+      </c>
+      <c r="L33" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="M33" t="n">
+        <v>29.44681344878295</v>
+      </c>
+      <c r="N33" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1982,46 +2029,47 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(10, 25, 75)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="F34" t="n">
-        <v>4.344774433853562</v>
+        <v>-24.23059717721926</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2.17%</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>43,448円</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.62%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.931946045277664</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-242305.9717721926</v>
+      </c>
+      <c r="J34" t="n">
+        <v>757694.0282278074</v>
+      </c>
+      <c r="K34" t="n">
+        <v>49901.80112859364</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>34.77764867317716</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2029,46 +2077,47 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-25.41140730782043</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-1.058808637825851</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-254114.0730782043</v>
+      </c>
+      <c r="J35" t="n">
+        <v>745885.9269217957</v>
+      </c>
+      <c r="K35" t="n">
+        <v>41550.49151444375</v>
+      </c>
+      <c r="L35" t="n">
+        <v>6.416666666666667</v>
+      </c>
+      <c r="M35" t="n">
+        <v>25.41140730782043</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2076,46 +2125,47 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-26.67047873205129</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-1.025787643540434</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-266704.7873205129</v>
+      </c>
+      <c r="J36" t="n">
+        <v>733295.2126794871</v>
+      </c>
+      <c r="K36" t="n">
+        <v>48542.62181860367</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.038461538461538</v>
+      </c>
+      <c r="M36" t="n">
+        <v>36.8779003055847</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2123,46 +2173,47 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 25, 75)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-26.68270284786781</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.067308113914712</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-266827.0284786781</v>
+      </c>
+      <c r="J37" t="n">
+        <v>733172.9715213219</v>
+      </c>
+      <c r="K37" t="n">
+        <v>45042.80610571041</v>
+      </c>
+      <c r="L37" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="M37" t="n">
+        <v>28.63819812005169</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2170,46 +2221,47 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-26.93267994341612</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1.122194997642338</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-269326.7994341612</v>
+      </c>
+      <c r="J38" t="n">
+        <v>730673.2005658388</v>
+      </c>
+      <c r="K38" t="n">
+        <v>43672.42432625835</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.833333333333333</v>
+      </c>
+      <c r="M38" t="n">
+        <v>31.96760478075084</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2217,46 +2269,47 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 30, 90)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-27.63862640303849</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-1.151609433459937</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-276386.2640303848</v>
+      </c>
+      <c r="J39" t="n">
+        <v>723613.7359696152</v>
+      </c>
+      <c r="K39" t="n">
+        <v>40699.46526110327</v>
+      </c>
+      <c r="L39" t="n">
+        <v>6.541666666666667</v>
+      </c>
+      <c r="M39" t="n">
+        <v>27.63862640303849</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2273,37 +2326,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-27.63862640303849</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-1.151609433459937</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-276386.2640303848</v>
+      </c>
+      <c r="J40" t="n">
+        <v>723613.7359696152</v>
+      </c>
+      <c r="K40" t="n">
+        <v>40699.46526110327</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.541666666666667</v>
+      </c>
+      <c r="M40" t="n">
+        <v>27.63862640303849</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2315,42 +2369,43 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(10, 30, 90)</t>
+          <t>(5, 20, 60)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-29.04855492480573</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-1.117252112492528</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-290485.5492480573</v>
+      </c>
+      <c r="J41" t="n">
+        <v>709514.4507519427</v>
+      </c>
+      <c r="K41" t="n">
+        <v>46424.27034011864</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.615384615384615</v>
+      </c>
+      <c r="M41" t="n">
+        <v>34.4049224934387</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2362,42 +2417,43 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>(50, 60)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-29.28555062505581</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-1.220231276043992</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-292855.5062505581</v>
+      </c>
+      <c r="J42" t="n">
+        <v>707144.4937494419</v>
+      </c>
+      <c r="K42" t="n">
+        <v>42433.10395902667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7.875</v>
+      </c>
+      <c r="M42" t="n">
+        <v>34.15834378676796</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2405,7 +2461,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2414,37 +2470,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>(55, 65)</t>
+          <t>(60, 70)</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.6151645207439198</v>
+        <v>-29.73757543431323</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-0.62%</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>-6,152円</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-1.56513554917438</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-297375.7543431323</v>
+      </c>
+      <c r="J43" t="n">
+        <v>702624.2456568677</v>
+      </c>
+      <c r="K43" t="n">
+        <v>31626.06931290748</v>
+      </c>
+      <c r="L43" t="n">
+        <v>6.947368421052632</v>
+      </c>
+      <c r="M43" t="n">
+        <v>29.73757543431323</v>
+      </c>
+      <c r="N43" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2456,7 +2513,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(20, 50, 100)</t>
+          <t>(10, 25, 75)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2465,33 +2522,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="F44" t="n">
-        <v>-7.791345898593045</v>
+        <v>-31.57882004280937</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>-7.79%</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>-77,913円</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>12日</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1.31578416845039</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-315788.2004280937</v>
+      </c>
+      <c r="J44" t="n">
+        <v>684211.7995719063</v>
+      </c>
+      <c r="K44" t="n">
+        <v>40538.37110031569</v>
+      </c>
+      <c r="L44" t="n">
+        <v>7.416666666666667</v>
+      </c>
+      <c r="M44" t="n">
+        <v>31.57882004280937</v>
+      </c>
+      <c r="N44" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2512,33 +2570,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="F45" t="n">
-        <v>-10.60525617202017</v>
+        <v>-31.83561493366178</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-10.61%</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-106,053円</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>13日</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.675558680719041</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-318356.1493366178</v>
+      </c>
+      <c r="J45" t="n">
+        <v>681643.8506633822</v>
+      </c>
+      <c r="K45" t="n">
+        <v>31011.45367809226</v>
+      </c>
+      <c r="L45" t="n">
+        <v>7.105263157894737</v>
+      </c>
+      <c r="M45" t="n">
+        <v>31.83561493366178</v>
+      </c>
+      <c r="N45" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2559,33 +2618,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="F46" t="n">
-        <v>-13.59171754711972</v>
+        <v>-31.83561493366178</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-13.59%</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>-135,917円</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>22日</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.675558680719041</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-318356.1493366178</v>
+      </c>
+      <c r="J46" t="n">
+        <v>681643.8506633822</v>
+      </c>
+      <c r="K46" t="n">
+        <v>31011.45367809226</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7.105263157894737</v>
+      </c>
+      <c r="M46" t="n">
+        <v>31.83561493366178</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/8035.T_settings.xlsx
+++ b/8035.T_settings.xlsx
@@ -509,28 +509,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F2" t="n">
-        <v>38.20006315091974</v>
+        <v>38.20006605738117</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>4.244451461213305</v>
+        <v>4.244451784153464</v>
       </c>
       <c r="I2" t="n">
-        <v>382000.6315091974</v>
+        <v>382000.6605738117</v>
       </c>
       <c r="J2" t="n">
-        <v>1382000.631509197</v>
+        <v>1382000.660573812</v>
       </c>
       <c r="K2" t="n">
-        <v>18266.8790059359</v>
+        <v>18266.87927233734</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>14.29560188636126</v>
+        <v>14.29560679826007</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -557,28 +557,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F3" t="n">
-        <v>38.06323721854407</v>
+        <v>38.06325136593946</v>
       </c>
       <c r="G3" t="n">
         <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>4.229248579838231</v>
+        <v>4.229250151771051</v>
       </c>
       <c r="I3" t="n">
-        <v>380632.3721854407</v>
+        <v>380632.5136593946</v>
       </c>
       <c r="J3" t="n">
-        <v>1380632.372185441</v>
+        <v>1380632.513659395</v>
       </c>
       <c r="K3" t="n">
-        <v>18255.30263463021</v>
+        <v>18255.30385222146</v>
       </c>
       <c r="L3" t="n">
         <v>10.11111111111111</v>
       </c>
       <c r="M3" t="n">
-        <v>14.380454120964</v>
+        <v>14.38045205518076</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -605,28 +605,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F4" t="n">
-        <v>38.06323721854407</v>
+        <v>38.06325136593946</v>
       </c>
       <c r="G4" t="n">
         <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>4.229248579838231</v>
+        <v>4.229250151771051</v>
       </c>
       <c r="I4" t="n">
-        <v>380632.3721854407</v>
+        <v>380632.5136593946</v>
       </c>
       <c r="J4" t="n">
-        <v>1380632.372185441</v>
+        <v>1380632.513659395</v>
       </c>
       <c r="K4" t="n">
-        <v>18255.30263463021</v>
+        <v>18255.30385222146</v>
       </c>
       <c r="L4" t="n">
         <v>10.11111111111111</v>
       </c>
       <c r="M4" t="n">
-        <v>14.380454120964</v>
+        <v>14.38045205518076</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -653,28 +653,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F5" t="n">
-        <v>34.07345436450285</v>
+        <v>34.0734300702594</v>
       </c>
       <c r="G5" t="n">
         <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.78593937383365</v>
+        <v>3.785936674473267</v>
       </c>
       <c r="I5" t="n">
-        <v>340734.5436450285</v>
+        <v>340734.300702594</v>
       </c>
       <c r="J5" t="n">
-        <v>1340734.543645028</v>
+        <v>1340734.300702594</v>
       </c>
       <c r="K5" t="n">
-        <v>17863.62056441342</v>
+        <v>17863.61818120418</v>
       </c>
       <c r="L5" t="n">
         <v>10.33333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>16.85470724584358</v>
+        <v>16.85472882569738</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -701,28 +701,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F6" t="n">
-        <v>34.07345436450285</v>
+        <v>34.0734300702594</v>
       </c>
       <c r="G6" t="n">
         <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>3.78593937383365</v>
+        <v>3.785936674473267</v>
       </c>
       <c r="I6" t="n">
-        <v>340734.5436450285</v>
+        <v>340734.300702594</v>
       </c>
       <c r="J6" t="n">
-        <v>1340734.543645028</v>
+        <v>1340734.300702594</v>
       </c>
       <c r="K6" t="n">
-        <v>17863.62056441342</v>
+        <v>17863.61818120418</v>
       </c>
       <c r="L6" t="n">
         <v>10.33333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>16.85470724584358</v>
+        <v>16.85472882569738</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -749,28 +749,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F7" t="n">
-        <v>33.94071400981706</v>
+        <v>33.94070064769906</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.771190445535229</v>
+        <v>3.771188960855451</v>
       </c>
       <c r="I7" t="n">
-        <v>339407.1400981706</v>
+        <v>339407.0064769906</v>
       </c>
       <c r="J7" t="n">
-        <v>1339407.140098171</v>
+        <v>1339407.006476991</v>
       </c>
       <c r="K7" t="n">
-        <v>17852.38985977717</v>
+        <v>17852.38840162655</v>
       </c>
       <c r="L7" t="n">
         <v>10.44444444444444</v>
       </c>
       <c r="M7" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N7" t="b">
         <v>1</v>
@@ -797,28 +797,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F8" t="n">
-        <v>33.94071400981706</v>
+        <v>33.94070064769906</v>
       </c>
       <c r="G8" t="n">
         <v>9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.771190445535229</v>
+        <v>3.771188960855451</v>
       </c>
       <c r="I8" t="n">
-        <v>339407.1400981706</v>
+        <v>339407.0064769906</v>
       </c>
       <c r="J8" t="n">
-        <v>1339407.140098171</v>
+        <v>1339407.006476991</v>
       </c>
       <c r="K8" t="n">
-        <v>17852.38985977717</v>
+        <v>17852.38840162655</v>
       </c>
       <c r="L8" t="n">
         <v>10.44444444444444</v>
       </c>
       <c r="M8" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>33.94071400981706</v>
+        <v>33.94070064769906</v>
       </c>
       <c r="G9" t="n">
         <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.771190445535229</v>
+        <v>3.771188960855451</v>
       </c>
       <c r="I9" t="n">
-        <v>339407.1400981706</v>
+        <v>339407.0064769906</v>
       </c>
       <c r="J9" t="n">
-        <v>1339407.140098171</v>
+        <v>1339407.006476991</v>
       </c>
       <c r="K9" t="n">
-        <v>17852.38985977717</v>
+        <v>17852.38840162655</v>
       </c>
       <c r="L9" t="n">
         <v>10.44444444444444</v>
       </c>
       <c r="M9" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -893,28 +893,28 @@
         <v>55.55555555555556</v>
       </c>
       <c r="F10" t="n">
-        <v>33.94071400981706</v>
+        <v>33.94070064769906</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.771190445535229</v>
+        <v>3.771188960855451</v>
       </c>
       <c r="I10" t="n">
-        <v>339407.1400981706</v>
+        <v>339407.0064769906</v>
       </c>
       <c r="J10" t="n">
-        <v>1339407.140098171</v>
+        <v>1339407.006476991</v>
       </c>
       <c r="K10" t="n">
-        <v>17852.38985977717</v>
+        <v>17852.38840162655</v>
       </c>
       <c r="L10" t="n">
         <v>10.44444444444444</v>
       </c>
       <c r="M10" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N10" t="b">
         <v>1</v>
@@ -941,28 +941,28 @@
         <v>50</v>
       </c>
       <c r="F11" t="n">
-        <v>30.03086691657931</v>
+        <v>30.0308802408945</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>3.753858364572414</v>
+        <v>3.753860030111813</v>
       </c>
       <c r="I11" t="n">
-        <v>300308.6691657931</v>
+        <v>300308.802408945</v>
       </c>
       <c r="J11" t="n">
-        <v>1300308.669165793</v>
+        <v>1300308.802408945</v>
       </c>
       <c r="K11" t="n">
-        <v>15946.10145062129</v>
+        <v>15946.10243158778</v>
       </c>
       <c r="L11" t="n">
         <v>9.875</v>
       </c>
       <c r="M11" t="n">
-        <v>14.380454120964</v>
+        <v>14.38045205518076</v>
       </c>
       <c r="N11" t="b">
         <v>1</v>
@@ -989,28 +989,28 @@
         <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>28.60481757528363</v>
+        <v>28.60480815390356</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>2.860481757528363</v>
+        <v>2.860480815390356</v>
       </c>
       <c r="I12" t="n">
-        <v>286048.1757528363</v>
+        <v>286048.0815390355</v>
       </c>
       <c r="J12" t="n">
-        <v>1286048.175752836</v>
+        <v>1286048.081539036</v>
       </c>
       <c r="K12" t="n">
-        <v>19408.64859621221</v>
+        <v>19408.64830049746</v>
       </c>
       <c r="L12" t="n">
         <v>9.6</v>
       </c>
       <c r="M12" t="n">
-        <v>14.56706195130362</v>
+        <v>14.56706820998191</v>
       </c>
       <c r="N12" t="b">
         <v>1</v>
@@ -1037,28 +1037,28 @@
         <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>26.14818766383985</v>
+        <v>26.14817507911545</v>
       </c>
       <c r="G13" t="n">
         <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>3.268523457979981</v>
+        <v>3.268521884889432</v>
       </c>
       <c r="I13" t="n">
-        <v>261481.8766383985</v>
+        <v>261481.7507911546</v>
       </c>
       <c r="J13" t="n">
-        <v>1261481.876638399</v>
+        <v>1261481.750791155</v>
       </c>
       <c r="K13" t="n">
-        <v>15612.14066955373</v>
+        <v>15612.13943489359</v>
       </c>
       <c r="L13" t="n">
         <v>10.25</v>
       </c>
       <c r="M13" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N13" t="b">
         <v>1</v>
@@ -1085,28 +1085,28 @@
         <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>26.14818766383985</v>
+        <v>26.14817507911545</v>
       </c>
       <c r="G14" t="n">
         <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>3.268523457979981</v>
+        <v>3.268521884889432</v>
       </c>
       <c r="I14" t="n">
-        <v>261481.8766383985</v>
+        <v>261481.7507911546</v>
       </c>
       <c r="J14" t="n">
-        <v>1261481.876638399</v>
+        <v>1261481.750791155</v>
       </c>
       <c r="K14" t="n">
-        <v>15612.14066955373</v>
+        <v>15612.13943489359</v>
       </c>
       <c r="L14" t="n">
         <v>10.25</v>
       </c>
       <c r="M14" t="n">
-        <v>16.93702582041117</v>
+        <v>16.93704061428817</v>
       </c>
       <c r="N14" t="b">
         <v>1</v>
@@ -1133,28 +1133,28 @@
         <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>24.76471969050802</v>
+        <v>24.76468531905313</v>
       </c>
       <c r="G15" t="n">
         <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>2.476471969050802</v>
+        <v>2.476468531905312</v>
       </c>
       <c r="I15" t="n">
-        <v>247647.1969050802</v>
+        <v>247646.8531905313</v>
       </c>
       <c r="J15" t="n">
-        <v>1247647.19690508</v>
+        <v>1247646.853190531</v>
       </c>
       <c r="K15" t="n">
-        <v>18971.29728732141</v>
+        <v>18971.29413477323</v>
       </c>
       <c r="L15" t="n">
         <v>9.9</v>
       </c>
       <c r="M15" t="n">
-        <v>17.11806160183318</v>
+        <v>17.11808443499317</v>
       </c>
       <c r="N15" t="b">
         <v>1</v>
@@ -1181,28 +1181,28 @@
         <v>50</v>
       </c>
       <c r="F16" t="n">
-        <v>24.76471969050802</v>
+        <v>24.76468531905313</v>
       </c>
       <c r="G16" t="n">
         <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>2.476471969050802</v>
+        <v>2.476468531905312</v>
       </c>
       <c r="I16" t="n">
-        <v>247647.1969050802</v>
+        <v>247646.8531905313</v>
       </c>
       <c r="J16" t="n">
-        <v>1247647.19690508</v>
+        <v>1247646.853190531</v>
       </c>
       <c r="K16" t="n">
-        <v>18971.29728732141</v>
+        <v>18971.29413477323</v>
       </c>
       <c r="L16" t="n">
         <v>9.9</v>
       </c>
       <c r="M16" t="n">
-        <v>17.11806160183318</v>
+        <v>17.11808443499317</v>
       </c>
       <c r="N16" t="b">
         <v>1</v>
@@ -1229,28 +1229,28 @@
         <v>38.88888888888889</v>
       </c>
       <c r="F17" t="n">
-        <v>11.46245750456799</v>
+        <v>11.46245113238534</v>
       </c>
       <c r="G17" t="n">
         <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6368031946982219</v>
+        <v>0.6368028406880745</v>
       </c>
       <c r="I17" t="n">
-        <v>114624.5750456799</v>
+        <v>114624.5113238534</v>
       </c>
       <c r="J17" t="n">
-        <v>1114624.57504568</v>
+        <v>1114624.511323853</v>
       </c>
       <c r="K17" t="n">
-        <v>34409.26109325193</v>
+        <v>34409.25885214727</v>
       </c>
       <c r="L17" t="n">
         <v>9.277777777777779</v>
       </c>
       <c r="M17" t="n">
-        <v>35.30659081991354</v>
+        <v>35.30659742483975</v>
       </c>
       <c r="N17" t="b">
         <v>1</v>
@@ -1277,28 +1277,28 @@
         <v>37.5</v>
       </c>
       <c r="F18" t="n">
-        <v>9.033069517362955</v>
+        <v>9.033085431074188</v>
       </c>
       <c r="G18" t="n">
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5645668448351847</v>
+        <v>0.5645678394421367</v>
       </c>
       <c r="I18" t="n">
-        <v>90330.69517362956</v>
+        <v>90330.85431074188</v>
       </c>
       <c r="J18" t="n">
-        <v>1090330.69517363</v>
+        <v>1090330.854310742</v>
       </c>
       <c r="K18" t="n">
-        <v>26942.44238292757</v>
+        <v>26942.44392077162</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
       </c>
       <c r="M18" t="n">
-        <v>31.33475137788361</v>
+        <v>31.33475203896299</v>
       </c>
       <c r="N18" t="b">
         <v>1</v>
@@ -1325,28 +1325,28 @@
         <v>38.88888888888889</v>
       </c>
       <c r="F19" t="n">
-        <v>7.873218058275408</v>
+        <v>7.873224438933748</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4374010032375227</v>
+        <v>0.4374013577185416</v>
       </c>
       <c r="I19" t="n">
-        <v>78732.18058275408</v>
+        <v>78732.24438933749</v>
       </c>
       <c r="J19" t="n">
-        <v>1078732.180582754</v>
+        <v>1078732.244389337</v>
       </c>
       <c r="K19" t="n">
-        <v>33550.6733925162</v>
+        <v>33550.67420806063</v>
       </c>
       <c r="L19" t="n">
         <v>9.333333333333334</v>
       </c>
       <c r="M19" t="n">
-        <v>37.38980467812942</v>
+        <v>37.38980378764609</v>
       </c>
       <c r="N19" t="b">
         <v>1</v>
@@ -1373,28 +1373,28 @@
         <v>37.5</v>
       </c>
       <c r="F20" t="n">
-        <v>7.594015899451007</v>
+        <v>7.594002469907189</v>
       </c>
       <c r="G20" t="n">
         <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4746259937156879</v>
+        <v>0.4746251543691993</v>
       </c>
       <c r="I20" t="n">
-        <v>75940.15899451007</v>
+        <v>75940.02469907189</v>
       </c>
       <c r="J20" t="n">
-        <v>1075940.15899451</v>
+        <v>1075940.024699072</v>
       </c>
       <c r="K20" t="n">
-        <v>28920.38345350993</v>
+        <v>28920.38210844105</v>
       </c>
       <c r="L20" t="n">
         <v>9.125</v>
       </c>
       <c r="M20" t="n">
-        <v>32.45245999312358</v>
+        <v>32.45247948994906</v>
       </c>
       <c r="N20" t="b">
         <v>1</v>
@@ -1421,28 +1421,28 @@
         <v>37.5</v>
       </c>
       <c r="F21" t="n">
-        <v>5.777377642685525</v>
+        <v>5.777371689664107</v>
       </c>
       <c r="G21" t="n">
         <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3610861026678453</v>
+        <v>0.3610857306040067</v>
       </c>
       <c r="I21" t="n">
-        <v>57773.77642685524</v>
+        <v>57773.71689664107</v>
       </c>
       <c r="J21" t="n">
-        <v>1057773.776426855</v>
+        <v>1057773.716896641</v>
       </c>
       <c r="K21" t="n">
-        <v>26472.44847657669</v>
+        <v>26472.44687797832</v>
       </c>
       <c r="L21" t="n">
         <v>7.6875</v>
       </c>
       <c r="M21" t="n">
-        <v>33.38507329398935</v>
+        <v>33.38508740698665</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -1469,28 +1469,28 @@
         <v>37.5</v>
       </c>
       <c r="F22" t="n">
-        <v>5.777377642685525</v>
+        <v>5.777371689664107</v>
       </c>
       <c r="G22" t="n">
         <v>16</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3610861026678453</v>
+        <v>0.3610857306040067</v>
       </c>
       <c r="I22" t="n">
-        <v>57773.77642685524</v>
+        <v>57773.71689664107</v>
       </c>
       <c r="J22" t="n">
-        <v>1057773.776426855</v>
+        <v>1057773.716896641</v>
       </c>
       <c r="K22" t="n">
-        <v>26472.44847657669</v>
+        <v>26472.44687797832</v>
       </c>
       <c r="L22" t="n">
         <v>7.6875</v>
       </c>
       <c r="M22" t="n">
-        <v>33.38507329398935</v>
+        <v>33.38508740698665</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -1517,28 +1517,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F23" t="n">
-        <v>4.90092899191645</v>
+        <v>4.900944302529096</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3500663565654607</v>
+        <v>0.3500674501806497</v>
       </c>
       <c r="I23" t="n">
-        <v>49009.2899191645</v>
+        <v>49009.44302529097</v>
       </c>
       <c r="J23" t="n">
-        <v>1049009.289919164</v>
+        <v>1049009.443025291</v>
       </c>
       <c r="K23" t="n">
-        <v>23555.25089685791</v>
+        <v>23555.25194033097</v>
       </c>
       <c r="L23" t="n">
         <v>8.214285714285714</v>
       </c>
       <c r="M23" t="n">
-        <v>31.33475137788361</v>
+        <v>31.33475203896299</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -1565,28 +1565,28 @@
         <v>33.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>4.374879535508051</v>
+        <v>4.37490510275428</v>
       </c>
       <c r="G24" t="n">
         <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2430488630837806</v>
+        <v>0.2430502834863489</v>
       </c>
       <c r="I24" t="n">
-        <v>43748.79535508051</v>
+        <v>43749.0510275428</v>
       </c>
       <c r="J24" t="n">
-        <v>1043748.795355081</v>
+        <v>1043749.051027543</v>
       </c>
       <c r="K24" t="n">
-        <v>31971.48741655216</v>
+        <v>31971.4910505737</v>
       </c>
       <c r="L24" t="n">
         <v>8.722222222222221</v>
       </c>
       <c r="M24" t="n">
-        <v>34.67898877759329</v>
+        <v>34.6789751731779</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -1613,28 +1613,28 @@
         <v>37.5</v>
       </c>
       <c r="F25" t="n">
-        <v>4.129345420285268</v>
+        <v>4.129344535356492</v>
       </c>
       <c r="G25" t="n">
         <v>16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2580840887678292</v>
+        <v>0.2580840334597808</v>
       </c>
       <c r="I25" t="n">
-        <v>41293.45420285268</v>
+        <v>41293.44535356492</v>
       </c>
       <c r="J25" t="n">
-        <v>1041293.454202853</v>
+        <v>1041293.445353565</v>
       </c>
       <c r="K25" t="n">
-        <v>28157.68041025702</v>
+        <v>28157.68178294248</v>
       </c>
       <c r="L25" t="n">
         <v>9.1875</v>
       </c>
       <c r="M25" t="n">
-        <v>34.62758066173772</v>
+        <v>34.62759192672105</v>
       </c>
       <c r="N25" t="b">
         <v>1</v>
@@ -1661,28 +1661,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F26" t="n">
-        <v>3.047774873863801</v>
+        <v>3.047781234586681</v>
       </c>
       <c r="G26" t="n">
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1792808749331647</v>
+        <v>0.1792812490933342</v>
       </c>
       <c r="I26" t="n">
-        <v>30477.74873863801</v>
+        <v>30477.81234586681</v>
       </c>
       <c r="J26" t="n">
-        <v>1030477.748738638</v>
+        <v>1030477.812345867</v>
       </c>
       <c r="K26" t="n">
-        <v>29885.15512715251</v>
+        <v>29885.15672744076</v>
       </c>
       <c r="L26" t="n">
         <v>9.235294117647058</v>
       </c>
       <c r="M26" t="n">
-        <v>35.30659081991354</v>
+        <v>35.30659742483977</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -1709,28 +1709,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F27" t="n">
-        <v>1.768621484874177</v>
+        <v>1.768615757460718</v>
       </c>
       <c r="G27" t="n">
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1263301060624412</v>
+        <v>0.1263296969614798</v>
       </c>
       <c r="I27" t="n">
-        <v>17686.21484874177</v>
+        <v>17686.15757460718</v>
       </c>
       <c r="J27" t="n">
-        <v>1017686.214848742</v>
+        <v>1017686.157574607</v>
       </c>
       <c r="K27" t="n">
-        <v>23186.39742292801</v>
+        <v>23186.39600926457</v>
       </c>
       <c r="L27" t="n">
         <v>8.428571428571429</v>
       </c>
       <c r="M27" t="n">
-        <v>33.38507329398935</v>
+        <v>33.38508740698665</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -1757,28 +1757,28 @@
         <v>35.71428571428572</v>
       </c>
       <c r="F28" t="n">
-        <v>1.768621484874177</v>
+        <v>1.768615757460718</v>
       </c>
       <c r="G28" t="n">
         <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1263301060624412</v>
+        <v>0.1263296969614798</v>
       </c>
       <c r="I28" t="n">
-        <v>17686.21484874177</v>
+        <v>17686.15757460718</v>
       </c>
       <c r="J28" t="n">
-        <v>1017686.214848742</v>
+        <v>1017686.157574607</v>
       </c>
       <c r="K28" t="n">
-        <v>23186.39742292801</v>
+        <v>23186.39600926457</v>
       </c>
       <c r="L28" t="n">
         <v>8.428571428571429</v>
       </c>
       <c r="M28" t="n">
-        <v>33.38507329398935</v>
+        <v>33.38508740698665</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -1805,28 +1805,28 @@
         <v>31.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7524210363520543</v>
+        <v>0.7524389005578822</v>
       </c>
       <c r="G29" t="n">
         <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>0.04702631477200339</v>
+        <v>0.04702743128486764</v>
       </c>
       <c r="I29" t="n">
-        <v>7524.210363520542</v>
+        <v>7524.389005578822</v>
       </c>
       <c r="J29" t="n">
-        <v>1007524.210363521</v>
+        <v>1007524.389005579</v>
       </c>
       <c r="K29" t="n">
-        <v>26772.15630211123</v>
+        <v>26772.16034856006</v>
       </c>
       <c r="L29" t="n">
         <v>8.5</v>
       </c>
       <c r="M29" t="n">
-        <v>31.79716953000986</v>
+        <v>31.79716804814567</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -1853,28 +1853,28 @@
         <v>35.29411764705883</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2705005949396058</v>
+        <v>-0.2704828386556706</v>
       </c>
       <c r="G30" t="n">
         <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01591179970232975</v>
+        <v>-0.01591075521503945</v>
       </c>
       <c r="I30" t="n">
-        <v>-2705.005949396058</v>
+        <v>-2704.828386556706</v>
       </c>
       <c r="J30" t="n">
-        <v>997294.9940506039</v>
+        <v>997295.1716134433</v>
       </c>
       <c r="K30" t="n">
-        <v>29091.38515225976</v>
+        <v>29091.3894840654</v>
       </c>
       <c r="L30" t="n">
         <v>9.294117647058824</v>
       </c>
       <c r="M30" t="n">
-        <v>37.38980467812942</v>
+        <v>37.38980378764606</v>
       </c>
       <c r="N30" t="b">
         <v>1</v>
@@ -1901,28 +1901,28 @@
         <v>29.41176470588236</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.504737562233431</v>
+        <v>-3.504702452354913</v>
       </c>
       <c r="G31" t="n">
         <v>17</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2061610330725548</v>
+        <v>-0.2061589677855831</v>
       </c>
       <c r="I31" t="n">
-        <v>-35047.37562233431</v>
+        <v>-35047.02452354913</v>
       </c>
       <c r="J31" t="n">
-        <v>964952.6243776657</v>
+        <v>964952.9754764509</v>
       </c>
       <c r="K31" t="n">
-        <v>27631.41733369237</v>
+        <v>27631.42409761628</v>
       </c>
       <c r="L31" t="n">
         <v>8.647058823529411</v>
       </c>
       <c r="M31" t="n">
-        <v>34.67898877759329</v>
+        <v>34.6789751731779</v>
       </c>
       <c r="N31" t="b">
         <v>1</v>
@@ -1949,28 +1949,28 @@
         <v>28</v>
       </c>
       <c r="F32" t="n">
-        <v>-21.7040919193398</v>
+        <v>-21.70411175970657</v>
       </c>
       <c r="G32" t="n">
         <v>25</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8681636767735919</v>
+        <v>-0.8681644703882629</v>
       </c>
       <c r="I32" t="n">
-        <v>-217040.919193398</v>
+        <v>-217041.1175970657</v>
       </c>
       <c r="J32" t="n">
-        <v>782959.080806602</v>
+        <v>782958.8824029343</v>
       </c>
       <c r="K32" t="n">
-        <v>48569.94437700919</v>
+        <v>48569.93434817639</v>
       </c>
       <c r="L32" t="n">
         <v>8.32</v>
       </c>
       <c r="M32" t="n">
-        <v>28.6381981200517</v>
+        <v>28.63819030972999</v>
       </c>
       <c r="N32" t="b">
         <v>1</v>
@@ -1997,28 +1997,28 @@
         <v>28</v>
       </c>
       <c r="F33" t="n">
-        <v>-24.22533050415007</v>
+        <v>-24.22534089189918</v>
       </c>
       <c r="G33" t="n">
         <v>25</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9690132201660029</v>
+        <v>-0.9690136356759672</v>
       </c>
       <c r="I33" t="n">
-        <v>-242253.3050415007</v>
+        <v>-242253.4089189918</v>
       </c>
       <c r="J33" t="n">
-        <v>757746.6949584993</v>
+        <v>757746.5910810082</v>
       </c>
       <c r="K33" t="n">
-        <v>47172.91696193137</v>
+        <v>47172.91211178736</v>
       </c>
       <c r="L33" t="n">
         <v>8.359999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>29.44681344878295</v>
+        <v>29.44680847522613</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -2045,28 +2045,28 @@
         <v>26.92307692307692</v>
       </c>
       <c r="F34" t="n">
-        <v>-24.23059717721926</v>
+        <v>-24.23064067073408</v>
       </c>
       <c r="G34" t="n">
         <v>26</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.931946045277664</v>
+        <v>-0.9319477181051568</v>
       </c>
       <c r="I34" t="n">
-        <v>-242305.9717721926</v>
+        <v>-242306.4067073407</v>
       </c>
       <c r="J34" t="n">
-        <v>757694.0282278074</v>
+        <v>757693.5932926593</v>
       </c>
       <c r="K34" t="n">
-        <v>49901.80112859364</v>
+        <v>49901.77737922835</v>
       </c>
       <c r="L34" t="n">
         <v>8</v>
       </c>
       <c r="M34" t="n">
-        <v>34.77764867317716</v>
+        <v>34.7776648189049</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -2093,28 +2093,28 @@
         <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>-25.41140730782043</v>
+        <v>-25.41141068754416</v>
       </c>
       <c r="G35" t="n">
         <v>24</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.058808637825851</v>
+        <v>-1.058808778647673</v>
       </c>
       <c r="I35" t="n">
-        <v>-254114.0730782043</v>
+        <v>-254114.1068754416</v>
       </c>
       <c r="J35" t="n">
-        <v>745885.9269217957</v>
+        <v>745885.8931245584</v>
       </c>
       <c r="K35" t="n">
-        <v>41550.49151444375</v>
+        <v>41550.48920466426</v>
       </c>
       <c r="L35" t="n">
         <v>6.416666666666667</v>
       </c>
       <c r="M35" t="n">
-        <v>25.41140730782043</v>
+        <v>25.41141068754416</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -2141,28 +2141,28 @@
         <v>26.92307692307692</v>
       </c>
       <c r="F36" t="n">
-        <v>-26.67047873205129</v>
+        <v>-26.67051229569388</v>
       </c>
       <c r="G36" t="n">
         <v>26</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.025787643540434</v>
+        <v>-1.025788934449765</v>
       </c>
       <c r="I36" t="n">
-        <v>-266704.7873205129</v>
+        <v>-266705.1229569388</v>
       </c>
       <c r="J36" t="n">
-        <v>733295.2126794871</v>
+        <v>733294.8770430612</v>
       </c>
       <c r="K36" t="n">
-        <v>48542.62181860367</v>
+        <v>48542.60352953147</v>
       </c>
       <c r="L36" t="n">
         <v>8.038461538461538</v>
       </c>
       <c r="M36" t="n">
-        <v>36.8779003055847</v>
+        <v>36.87790858935085</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -2189,28 +2189,28 @@
         <v>24</v>
       </c>
       <c r="F37" t="n">
-        <v>-26.68270284786781</v>
+        <v>-26.68269927671206</v>
       </c>
       <c r="G37" t="n">
         <v>25</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.067308113914712</v>
+        <v>-1.067307971068482</v>
       </c>
       <c r="I37" t="n">
-        <v>-266827.0284786781</v>
+        <v>-266826.9927671206</v>
       </c>
       <c r="J37" t="n">
-        <v>733172.9715213219</v>
+        <v>733173.0072328794</v>
       </c>
       <c r="K37" t="n">
-        <v>45042.80610571041</v>
+        <v>45042.80678627663</v>
       </c>
       <c r="L37" t="n">
         <v>7.92</v>
       </c>
       <c r="M37" t="n">
-        <v>28.63819812005169</v>
+        <v>28.63819030972995</v>
       </c>
       <c r="N37" t="b">
         <v>1</v>
@@ -2237,28 +2237,28 @@
         <v>25</v>
       </c>
       <c r="F38" t="n">
-        <v>-26.93267994341612</v>
+        <v>-26.93272087815339</v>
       </c>
       <c r="G38" t="n">
         <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.122194997642338</v>
+        <v>-1.122196703256391</v>
       </c>
       <c r="I38" t="n">
-        <v>-269326.7994341612</v>
+        <v>-269327.2087815339</v>
       </c>
       <c r="J38" t="n">
-        <v>730673.2005658388</v>
+        <v>730672.7912184661</v>
       </c>
       <c r="K38" t="n">
-        <v>43672.42432625835</v>
+        <v>43672.40445155089</v>
       </c>
       <c r="L38" t="n">
         <v>7.833333333333333</v>
       </c>
       <c r="M38" t="n">
-        <v>31.96760478075084</v>
+        <v>31.96762877252407</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
@@ -2285,28 +2285,28 @@
         <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>-27.63862640303849</v>
+        <v>-27.63864431602404</v>
       </c>
       <c r="G39" t="n">
         <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.151609433459937</v>
+        <v>-1.151610179834335</v>
       </c>
       <c r="I39" t="n">
-        <v>-276386.2640303848</v>
+        <v>-276386.4431602404</v>
       </c>
       <c r="J39" t="n">
-        <v>723613.7359696152</v>
+        <v>723613.5568397596</v>
       </c>
       <c r="K39" t="n">
-        <v>40699.46526110327</v>
+        <v>40699.45740155314</v>
       </c>
       <c r="L39" t="n">
         <v>6.541666666666667</v>
       </c>
       <c r="M39" t="n">
-        <v>27.63862640303849</v>
+        <v>27.63864431602404</v>
       </c>
       <c r="N39" t="b">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>-27.63862640303849</v>
+        <v>-27.63864431602404</v>
       </c>
       <c r="G40" t="n">
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.151609433459937</v>
+        <v>-1.151610179834335</v>
       </c>
       <c r="I40" t="n">
-        <v>-276386.2640303848</v>
+        <v>-276386.4431602404</v>
       </c>
       <c r="J40" t="n">
-        <v>723613.7359696152</v>
+        <v>723613.5568397596</v>
       </c>
       <c r="K40" t="n">
-        <v>40699.46526110327</v>
+        <v>40699.45740155314</v>
       </c>
       <c r="L40" t="n">
         <v>6.541666666666667</v>
       </c>
       <c r="M40" t="n">
-        <v>27.63862640303849</v>
+        <v>27.63864431602404</v>
       </c>
       <c r="N40" t="b">
         <v>1</v>
@@ -2381,28 +2381,28 @@
         <v>23.07692307692308</v>
       </c>
       <c r="F41" t="n">
-        <v>-29.04855492480573</v>
+        <v>-29.04857421751845</v>
       </c>
       <c r="G41" t="n">
         <v>26</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.117252112492528</v>
+        <v>-1.11725285451994</v>
       </c>
       <c r="I41" t="n">
-        <v>-290485.5492480573</v>
+        <v>-290485.7421751845</v>
       </c>
       <c r="J41" t="n">
-        <v>709514.4507519427</v>
+        <v>709514.2578248155</v>
       </c>
       <c r="K41" t="n">
-        <v>46424.27034011864</v>
+        <v>46424.25802353188</v>
       </c>
       <c r="L41" t="n">
         <v>7.615384615384615</v>
       </c>
       <c r="M41" t="n">
-        <v>34.4049224934387</v>
+        <v>34.40493253076455</v>
       </c>
       <c r="N41" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>-29.28555062505581</v>
+        <v>-29.28558201648891</v>
       </c>
       <c r="G42" t="n">
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.220231276043992</v>
+        <v>-1.220232584020371</v>
       </c>
       <c r="I42" t="n">
-        <v>-292855.5062505581</v>
+        <v>-292855.8201648891</v>
       </c>
       <c r="J42" t="n">
-        <v>707144.4937494419</v>
+        <v>707144.1798351109</v>
       </c>
       <c r="K42" t="n">
-        <v>42433.10395902667</v>
+        <v>42433.08902874654</v>
       </c>
       <c r="L42" t="n">
         <v>7.875</v>
       </c>
       <c r="M42" t="n">
-        <v>34.15834378676796</v>
+        <v>34.15835934760147</v>
       </c>
       <c r="N42" t="b">
         <v>1</v>
@@ -2477,28 +2477,28 @@
         <v>21.05263157894737</v>
       </c>
       <c r="F43" t="n">
-        <v>-29.73757543431323</v>
+        <v>-29.73759275907305</v>
       </c>
       <c r="G43" t="n">
         <v>19</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.56513554917438</v>
+        <v>-1.565136461003845</v>
       </c>
       <c r="I43" t="n">
-        <v>-297375.7543431323</v>
+        <v>-297375.9275907305</v>
       </c>
       <c r="J43" t="n">
-        <v>702624.2456568677</v>
+        <v>702624.0724092695</v>
       </c>
       <c r="K43" t="n">
-        <v>31626.06931290748</v>
+        <v>31626.0631547336</v>
       </c>
       <c r="L43" t="n">
         <v>6.947368421052632</v>
       </c>
       <c r="M43" t="n">
-        <v>29.73757543431323</v>
+        <v>29.73759275907305</v>
       </c>
       <c r="N43" t="b">
         <v>1</v>
@@ -2525,28 +2525,28 @@
         <v>20.83333333333334</v>
       </c>
       <c r="F44" t="n">
-        <v>-31.57882004280937</v>
+        <v>-31.57883770386908</v>
       </c>
       <c r="G44" t="n">
         <v>24</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.31578416845039</v>
+        <v>-1.315784904327878</v>
       </c>
       <c r="I44" t="n">
-        <v>-315788.2004280937</v>
+        <v>-315788.3770386908</v>
       </c>
       <c r="J44" t="n">
-        <v>684211.7995719063</v>
+        <v>684211.6229613092</v>
       </c>
       <c r="K44" t="n">
-        <v>40538.37110031569</v>
+        <v>40538.36178937349</v>
       </c>
       <c r="L44" t="n">
         <v>7.416666666666667</v>
       </c>
       <c r="M44" t="n">
-        <v>31.57882004280937</v>
+        <v>31.57883770386908</v>
       </c>
       <c r="N44" t="b">
         <v>1</v>
@@ -2573,28 +2573,28 @@
         <v>21.05263157894737</v>
       </c>
       <c r="F45" t="n">
-        <v>-31.83561493366178</v>
+        <v>-31.83564552649289</v>
       </c>
       <c r="G45" t="n">
         <v>19</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.675558680719041</v>
+        <v>-1.675560290868047</v>
       </c>
       <c r="I45" t="n">
-        <v>-318356.1493366178</v>
+        <v>-318356.4552649289</v>
       </c>
       <c r="J45" t="n">
-        <v>681643.8506633822</v>
+        <v>681643.5447350711</v>
       </c>
       <c r="K45" t="n">
-        <v>31011.45367809226</v>
+        <v>31011.44363170554</v>
       </c>
       <c r="L45" t="n">
         <v>7.105263157894737</v>
       </c>
       <c r="M45" t="n">
-        <v>31.83561493366178</v>
+        <v>31.83564552649289</v>
       </c>
       <c r="N45" t="b">
         <v>1</v>
@@ -2621,28 +2621,28 @@
         <v>21.05263157894737</v>
       </c>
       <c r="F46" t="n">
-        <v>-31.83561493366178</v>
+        <v>-31.83564552649289</v>
       </c>
       <c r="G46" t="n">
         <v>19</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.675558680719041</v>
+        <v>-1.675560290868047</v>
       </c>
       <c r="I46" t="n">
-        <v>-318356.1493366178</v>
+        <v>-318356.4552649289</v>
       </c>
       <c r="J46" t="n">
-        <v>681643.8506633822</v>
+        <v>681643.5447350711</v>
       </c>
       <c r="K46" t="n">
-        <v>31011.45367809226</v>
+        <v>31011.44363170554</v>
       </c>
       <c r="L46" t="n">
         <v>7.105263157894737</v>
       </c>
       <c r="M46" t="n">
-        <v>31.83561493366178</v>
+        <v>31.83564552649289</v>
       </c>
       <c r="N46" t="b">
         <v>1</v>
